--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:38+00:00</t>
+    <t>2026-05-03T21:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T21:28:00+00:00</t>
+    <t>2026-05-04T06:23:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:23:23+00:00</t>
+    <t>2026-05-04T06:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:44:52+00:00</t>
+    <t>2026-05-04T07:06:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:06:34+00:00</t>
+    <t>2026-05-04T07:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:30:32+00:00</t>
+    <t>2026-05-04T07:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:50:36+00:00</t>
+    <t>2026-05-04T08:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:11:13+00:00</t>
+    <t>2026-05-04T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:32:13+00:00</t>
+    <t>2026-05-04T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:30:07+00:00</t>
+    <t>2026-05-04T09:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:51:52+00:00</t>
+    <t>2026-05-04T11:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:25:12+00:00</t>
+    <t>2026-05-04T11:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:47:21+00:00</t>
+    <t>2026-05-04T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:11:06+00:00</t>
+    <t>2026-05-04T13:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:22:07+00:00</t>
+    <t>2026-05-04T13:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:47:49+00:00</t>
+    <t>2026-05-04T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:15:24+00:00</t>
+    <t>2026-05-04T14:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:55:41+00:00</t>
+    <t>2026-05-04T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T15:18:17+00:00</t>
+    <t>2026-05-04T15:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T18:43:40+00:00</t>
+    <t>2026-05-12T08:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
+++ b/ci-build/StructureDefinition-senologie-nebenwirkung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$80</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2848" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3008" uniqueCount="420">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:39:42+00:00</t>
+    <t>2026-05-12T14:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -235,6 +235,12 @@
   </si>
   <si>
     <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: BIH LM Senologie</t>
+  </si>
+  <si>
+    <t>Mapping: LM-Element: Nebenwirkung</t>
   </si>
   <si>
     <t>Mapping: Mapping FHIR zu oBDS</t>
@@ -1631,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM80"/>
+  <dimension ref="A1:AO80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.7109375" customWidth="true" bestFit="true"/>
@@ -1669,9 +1675,11 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="30.08203125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.35546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="34.36328125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="30.08203125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1792,6 +1800,12 @@
       <c r="AM1" t="s" s="1">
         <v>75</v>
       </c>
+      <c r="AN1" t="s" s="1">
+        <v>76</v>
+      </c>
+      <c r="AO1" t="s" s="1">
+        <v>77</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1802,14 +1816,14 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1821,13 +1835,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1881,16 +1895,16 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>20</v>
@@ -1899,15 +1913,21 @@
         <v>20</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>83</v>
+        <v>20</v>
+      </c>
+      <c r="AN2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO2" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1915,10 +1935,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1927,19 +1947,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1989,13 +2009,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2010,15 +2030,21 @@
         <v>20</v>
       </c>
       <c r="AM3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO3" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2026,10 +2052,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2038,16 +2064,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2098,19 +2124,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2119,15 +2145,21 @@
         <v>20</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO4" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2135,10 +2167,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
@@ -2150,13 +2182,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2207,13 +2239,13 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
@@ -2228,26 +2260,32 @@
         <v>20</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO5" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2259,16 +2297,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2306,31 +2344,31 @@
         <v>20</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2339,15 +2377,21 @@
         <v>20</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO6" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2355,10 +2399,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2367,19 +2411,19 @@
         <v>20</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2429,19 +2473,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2450,15 +2494,21 @@
         <v>20</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2466,10 +2516,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2478,19 +2528,19 @@
         <v>20</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2540,19 +2590,19 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>20</v>
@@ -2561,15 +2611,21 @@
         <v>20</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2577,10 +2633,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2589,19 +2645,19 @@
         <v>20</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2651,19 +2707,19 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2672,15 +2728,21 @@
         <v>20</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2688,31 +2750,31 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2762,19 +2824,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2783,15 +2845,21 @@
         <v>20</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2799,10 +2867,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -2811,19 +2879,19 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2849,13 +2917,13 @@
         <v>20</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>20</v>
@@ -2873,19 +2941,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -2894,15 +2962,21 @@
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
+      </c>
+      <c r="AN11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>151</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2910,10 +2984,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2922,19 +2996,19 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2960,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -2984,19 +3058,19 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -3005,15 +3079,21 @@
         <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>151</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3021,31 +3101,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3095,19 +3175,19 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
@@ -3116,15 +3196,21 @@
         <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3132,10 +3218,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3147,16 +3233,16 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3182,13 +3268,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3206,19 +3292,19 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
@@ -3227,26 +3313,32 @@
         <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3258,16 +3350,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3317,19 +3409,19 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -3338,26 +3430,32 @@
         <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>179</v>
+        <v>20</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>181</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3369,16 +3467,16 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3428,13 +3526,13 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
@@ -3449,26 +3547,32 @@
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3480,16 +3584,16 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3527,31 +3631,31 @@
         <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -3560,50 +3664,56 @@
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3640,31 +3750,31 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -3673,15 +3783,21 @@
         <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3689,10 +3805,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3701,22 +3817,22 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3765,19 +3881,19 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
@@ -3786,15 +3902,21 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>201</v>
+        <v>20</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>203</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3802,31 +3924,31 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3834,7 +3956,7 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>20</v>
@@ -3852,13 +3974,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3876,36 +3998,42 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3913,10 +4041,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3925,19 +4053,19 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3963,13 +4091,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -3987,36 +4115,42 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>218</v>
+        <v>20</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>220</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4024,31 +4158,31 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4074,13 +4208,13 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
@@ -4098,36 +4232,42 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>218</v>
+        <v>20</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>220</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4135,10 +4275,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4150,13 +4290,13 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4207,13 +4347,13 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -4228,26 +4368,32 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4259,16 +4405,16 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4306,31 +4452,31 @@
         <v>20</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -4339,15 +4485,21 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4355,34 +4507,34 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4407,39 +4559,39 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -4448,15 +4600,21 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>237</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4464,10 +4622,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4479,13 +4637,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4536,13 +4694,13 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
@@ -4557,26 +4715,32 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4588,16 +4752,16 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4635,31 +4799,31 @@
         <v>20</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -4668,15 +4832,21 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4684,34 +4854,34 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4760,19 +4930,19 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -4781,15 +4951,21 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>244</v>
+        <v>20</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>246</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4797,31 +4973,31 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4871,36 +5047,42 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>253</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4908,34 +5090,34 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -4984,36 +5166,42 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>260</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5021,10 +5209,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5033,22 +5221,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5097,19 +5285,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5118,15 +5306,21 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>266</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5134,10 +5328,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5146,22 +5340,22 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5210,19 +5404,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5231,52 +5425,58 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>274</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5325,19 +5525,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -5346,15 +5546,21 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>237</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5362,10 +5568,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5377,13 +5583,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5434,13 +5640,13 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -5455,26 +5661,32 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5486,16 +5698,16 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5533,31 +5745,31 @@
         <v>20</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -5566,15 +5778,21 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5582,34 +5800,34 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5619,7 +5837,7 @@
         <v>20</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>20</v>
@@ -5658,19 +5876,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -5679,15 +5897,21 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>244</v>
+        <v>20</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>246</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5695,31 +5919,31 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5769,19 +5993,19 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -5790,15 +6014,21 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>251</v>
+        <v>20</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>253</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5806,34 +6036,34 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -5882,19 +6112,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -5903,15 +6133,21 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>258</v>
+        <v>20</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>260</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5919,10 +6155,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -5931,22 +6167,22 @@
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -5995,19 +6231,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6016,15 +6252,21 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>266</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6032,10 +6274,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6044,22 +6286,22 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6108,19 +6350,19 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -6129,15 +6371,21 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>274</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6145,34 +6393,34 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6221,19 +6469,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -6242,50 +6490,56 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>295</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6334,36 +6588,42 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>302</v>
+        <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6371,31 +6631,31 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6445,36 +6705,42 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>309</v>
+        <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6482,28 +6748,28 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6554,36 +6820,42 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6591,10 +6863,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6603,16 +6875,16 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6663,19 +6935,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -6684,15 +6956,21 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6700,10 +6978,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -6712,19 +6990,19 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6774,36 +7052,42 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6811,10 +7095,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -6823,19 +7107,19 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6885,19 +7169,19 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -6906,15 +7190,21 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6922,10 +7212,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -6934,19 +7224,19 @@
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6996,19 +7286,19 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7017,15 +7307,21 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7033,31 +7329,31 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7083,13 +7379,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7107,36 +7403,42 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>337</v>
+        <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>218</v>
+        <v>339</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>220</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7144,10 +7446,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7159,13 +7461,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7216,13 +7518,13 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
@@ -7237,26 +7539,32 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7268,16 +7576,16 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7315,31 +7623,31 @@
         <v>20</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -7348,15 +7656,21 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7364,34 +7678,34 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7440,19 +7754,19 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -7461,15 +7775,21 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>237</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7477,10 +7797,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -7492,13 +7812,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7549,13 +7869,13 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
@@ -7570,26 +7890,32 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -7601,16 +7927,16 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7648,31 +7974,31 @@
         <v>20</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -7681,15 +8007,21 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7697,34 +8029,34 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -7773,19 +8105,19 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -7794,15 +8126,21 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>244</v>
+        <v>20</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>246</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7810,10 +8148,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -7822,19 +8160,19 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7884,19 +8222,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -7905,15 +8243,21 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>251</v>
+        <v>20</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>253</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7921,34 +8265,34 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -7997,19 +8341,19 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
@@ -8018,15 +8362,21 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>258</v>
+        <v>20</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>260</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8034,10 +8384,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -8046,22 +8396,22 @@
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -8110,19 +8460,19 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -8131,15 +8481,21 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>266</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8147,10 +8503,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -8159,22 +8515,22 @@
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8223,19 +8579,19 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -8244,15 +8600,21 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>274</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8260,34 +8622,34 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -8336,19 +8698,19 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
@@ -8357,15 +8719,21 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>295</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8373,10 +8741,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -8385,19 +8753,19 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8423,13 +8791,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -8447,19 +8815,19 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
@@ -8468,15 +8836,21 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>218</v>
+        <v>20</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>220</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8484,10 +8858,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -8496,19 +8870,19 @@
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8534,13 +8908,13 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -8558,19 +8932,19 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
@@ -8579,15 +8953,21 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>218</v>
+        <v>20</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>220</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8595,10 +8975,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -8607,19 +8987,19 @@
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8669,36 +9049,42 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>365</v>
+        <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8706,10 +9092,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -8718,19 +9104,19 @@
         <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8780,19 +9166,19 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
@@ -8801,15 +9187,21 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8817,28 +9209,28 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8889,19 +9281,19 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -8910,15 +9302,21 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8926,10 +9324,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -8941,13 +9339,13 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8998,13 +9396,13 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
@@ -9019,26 +9417,32 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -9050,16 +9454,16 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9097,31 +9501,31 @@
         <v>20</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
@@ -9130,50 +9534,56 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -9222,19 +9632,19 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
@@ -9243,47 +9653,53 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9333,19 +9749,19 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>20</v>
@@ -9354,15 +9770,21 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9370,10 +9792,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -9382,16 +9804,16 @@
         <v>20</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9442,19 +9864,19 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
@@ -9463,15 +9885,21 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9479,10 +9907,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -9494,13 +9922,13 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9551,13 +9979,13 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
@@ -9572,26 +10000,32 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
@@ -9603,16 +10037,16 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9650,31 +10084,31 @@
         <v>20</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>20</v>
@@ -9683,50 +10117,56 @@
         <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -9775,19 +10215,19 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>20</v>
@@ -9796,15 +10236,21 @@
         <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9812,10 +10258,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
@@ -9824,19 +10270,19 @@
         <v>20</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9862,13 +10308,13 @@
         <v>20</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>20</v>
@@ -9886,19 +10332,19 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
@@ -9907,15 +10353,21 @@
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>218</v>
+        <v>20</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>220</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9923,10 +10375,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>20</v>
@@ -9935,19 +10387,19 @@
         <v>20</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9997,19 +10449,19 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>20</v>
@@ -10018,15 +10470,21 @@
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10034,10 +10492,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
@@ -10046,19 +10504,19 @@
         <v>20</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10108,19 +10566,19 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>20</v>
@@ -10129,15 +10587,21 @@
         <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10145,10 +10609,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -10157,19 +10621,19 @@
         <v>20</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10195,13 +10659,13 @@
         <v>20</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>20</v>
@@ -10219,19 +10683,19 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>20</v>
@@ -10240,15 +10704,21 @@
         <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>218</v>
+        <v>20</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>220</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10256,10 +10726,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>20</v>
@@ -10268,19 +10738,19 @@
         <v>20</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10330,19 +10800,19 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>20</v>
@@ -10351,15 +10821,21 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10367,10 +10843,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>20</v>
@@ -10379,19 +10855,19 @@
         <v>20</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10441,19 +10917,19 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>20</v>
@@ -10462,15 +10938,21 @@
         <v>20</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10478,10 +10960,10 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>20</v>
@@ -10490,19 +10972,19 @@
         <v>20</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10552,19 +11034,19 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>20</v>
@@ -10573,11 +11055,17 @@
         <v>20</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM80">
+  <autoFilter ref="A1:AO80">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
